--- a/mls_urls.xlsx
+++ b/mls_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="1045">
   <si>
     <t>x</t>
   </si>
@@ -1199,10 +1199,394 @@
     <t>394</t>
   </si>
   <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>455</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>466</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>497</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6b8eefb5/Inter-Miami-Real-Salt-Lake-February-21-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2d02571f/Los-Angeles-FC-Seattle-Sounders-FC-February-24-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/2d02571f/Los-Angeles-FC-Seattle-Sounders-February-24-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/50d19f80/Columbus-Crew-Atlanta-United-February-24-2024-Major-League-Soccer</t>
@@ -1214,33 +1598,33 @@
     <t>https://fbref.com/en/matches/58d9874f/Nashville-SC-New-York-Red-Bulls-February-25-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/82e1e5b8/Austin-FC-Minnesota-United-February-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8c354a46/Orlando-City-CF-Montreal-February-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/24530d12/Portland-Timbers-Colorado-Rapids-February-24-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e2c29bd6/Houston-Dynamo-Sporting-Kansas-City-February-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/25e841a5/Philadelphia-Union-Chicago-Fire-February-24-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b1ee8936/FC-Dallas-San-Jose-Earthquakes-February-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4ca51dbf/St-Louis-City-Real-Salt-Lake-February-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4a63fe1b/DC-United-New-England-Revolution-February-24-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4ca51dbf/St-Louis-City-Real-Salt-Lake-February-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/82e1e5b8/Austin-FC-Minnesota-United-February-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8c354a46/Orlando-City-CF-Montreal-February-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b1ee8936/FC-Dallas-San-Jose-Earthquakes-February-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c83d7bed/Charlotte-FC-New-York-City-FC-February-24-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e2c29bd6/Houston-Dynamo-Sporting-Kansas-City-February-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/109611b3/LA-Galaxy-Inter-Miami-February-25-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -1262,30 +1646,30 @@
     <t>https://fbref.com/en/matches/015cc6b8/Houston-Dynamo-New-York-Red-Bulls-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5c115e9a/Chicago-Fire-FC-Cincinnati-March-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0305a9cf/St-Louis-City-New-York-City-FC-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/15730afc/FC-Dallas-CF-Montreal-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e6fc6e27/Portland-Timbers-DC-United-March-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/33dbf3d5/Sporting-Kansas-City-Philadelphia-Union-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5c115e9a/Chicago-Fire-FC-Cincinnati-March-2-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/d38f35bb/Seattle-Sounders-Austin-FC-March-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e3a4e251/Colorado-Rapids-Nashville-SC-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/ce1527df/California-Clasico-San-Jose-Earthquakes-LA-Galaxy-March-2-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d38f35bb/Seattle-Sounders-FC-Austin-FC-March-2-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e3a4e251/Colorado-Rapids-Nashville-SC-March-2-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e6fc6e27/Portland-Timbers-DC-United-March-2-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1626c4bb/Toronto-FC-Charlotte-FC-March-9-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -1301,31 +1685,31 @@
     <t>https://fbref.com/en/matches/b1553752/Inter-Miami-CF-Montreal-March-10-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/560f62ab/San-Jose-Earthquakes-Vancouver-Whitecaps-FC-March-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cd6b54bb/Real-Salt-Lake-Colorado-Rapids-March-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c9af7eff/Austin-FC-St-Louis-City-March-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4274e2ff/Columbus-Crew-Chicago-Fire-March-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3b4354d9/Orlando-City-Minnesota-United-March-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/22efe495/Atlanta-United-New-England-Revolution-March-9-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/290d6c0d/New-York-Red-Bulls-FC-Dallas-March-9-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3b4354d9/Orlando-City-Minnesota-United-March-9-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4274e2ff/Columbus-Crew-Chicago-Fire-March-9-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/560f62ab/San-Jose-Earthquakes-Vancouver-Whitecaps-FC-March-9-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c9af7eff/Austin-FC-St-Louis-City-March-9-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cd6b54bb/Real-Salt-Lake-Colorado-Rapids-March-9-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f0a93403/Los-Angeles-FC-Sporting-Kansas-City-March-9-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9cdfdcac/Seattle-Sounders-FC-Colorado-Rapids-March-16-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/9cdfdcac/Seattle-Sounders-Colorado-Rapids-March-16-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/ebdee699/Chicago-Fire-CF-Montreal-March-16-2024-Major-League-Soccer</t>
@@ -1334,12 +1718,12 @@
     <t>https://fbref.com/en/matches/1bc74dac/DC-United-Inter-Miami-March-16-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a953c4ca/Columbus-Crew-New-York-Red-Bulls-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/44aa0fbf/New-York-City-FC-Toronto-FC-March-16-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a953c4ca/Columbus-Crew-New-York-Red-Bulls-March-16-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8a1b90c6/New-England-Revolution-FC-Cincinnati-March-17-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -1349,30 +1733,30 @@
     <t>https://fbref.com/en/matches/21fafab2/Houston-Dynamo-Portland-Timbers-March-16-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ce241944/Nashville-SC-Charlotte-FC-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e0d5cb27/Austin-FC-Philadelphia-Union-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a6734d95/Sporting-Kansas-City-San-Jose-Earthquakes-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/55a8dc23/Minnesota-United-Los-Angeles-FC-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca9b30e2/LA-Galaxy-St-Louis-City-March-16-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/288fcaab/FC-Dallas-Vancouver-Whitecaps-FC-March-16-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/55a8dc23/Minnesota-United-Los-Angeles-FC-March-16-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a6734d95/Sporting-Kansas-City-San-Jose-Earthquakes-March-16-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ca9b30e2/LA-Galaxy-St-Louis-City-March-16-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce241944/Nashville-SC-Charlotte-FC-March-16-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e0d5cb27/Austin-FC-Philadelphia-Union-March-16-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/923922fd/New-England-Revolution-Chicago-Fire-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7e276e42/New-York-Red-Bulls-Inter-Miami-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/923922fd/New-England-Revolution-Chicago-Fire-March-23-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/beeb3325/Vancouver-Whitecaps-FC-Real-Salt-Lake-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -1382,72 +1766,72 @@
     <t>https://fbref.com/en/matches/909fab57/Orlando-City-Austin-FC-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f92c125a/FC-Cincinnati-New-York-City-FC-March-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ab42cb3e/Toronto-FC-Atlanta-United-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f92c125a/FC-Cincinnati-New-York-City-FC-March-23-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/ea230f1a/San-Jose-Earthquakes-Seattle-Sounders-March-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7402934b/Colorado-Rapids-Houston-Dynamo-March-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/69df8cd0/Sporting-Kansas-City-LA-Galaxy-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2d05cf5f/Portland-Timbers-Philadelphia-Union-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/69df8cd0/Sporting-Kansas-City-LA-Galaxy-March-23-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7402934b/Colorado-Rapids-Houston-Dynamo-March-23-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/fb236b9c/Los-Angeles-FC-Nashville-SC-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9b3a4ec5/St-Louis-City-DC-United-March-23-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ea230f1a/San-Jose-Earthquakes-Seattle-Sounders-FC-March-23-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fb236b9c/Los-Angeles-FC-Nashville-SC-March-23-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/151503a3/Colorado-Rapids-Los-Angeles-FC-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2ff313cf/Philadelphia-Union-Minnesota-United-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/86ee1038/Inter-Miami-New-York-City-FC-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f08c8327/Charlotte-FC-FC-Cincinnati-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a2da36ff/DC-United-CF-Montreal-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/19d23a79/Toronto-FC-Sporting-Kansas-City-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/86ee1038/Inter-Miami-New-York-City-FC-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8d190635/Orlando-City-New-York-Red-Bulls-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a2da36ff/DC-United-CF-Montreal-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f08c8327/Charlotte-FC-FC-Cincinnati-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/afc6625d/Atlanta-United-Chicago-Fire-March-31-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f8a4be2d/LA-Galaxy-Seattle-Sounders-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8bb08620/Real-Salt-Lake-St-Louis-City-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47c385e1/Austin-FC-FC-Dallas-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/28f83b14/Vancouver-Whitecaps-FC-Portland-Timbers-March-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/22e49f68/Houston-Dynamo-San-Jose-Earthquakes-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/28f83b14/Vancouver-Whitecaps-FC-Portland-Timbers-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/41aebff4/Nashville-SC-Columbus-Crew-March-30-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/47c385e1/Austin-FC-FC-Dallas-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8bb08620/Real-Salt-Lake-St-Louis-City-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f8a4be2d/LA-Galaxy-Seattle-Sounders-FC-March-30-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f1c67d3f/Vancouver-Whitecaps-FC-Toronto-FC-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -1457,310 +1841,316 @@
     <t>https://fbref.com/en/matches/2fbde7c7/Columbus-Crew-DC-United-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/eee99db7/FC-Cincinnati-New-York-Red-Bulls-April-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/d04ed97c/Inter-Miami-Colorado-Rapids-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f80d3365/New-England-Revolution-Charlotte-FC-April-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/df1be9b7/New-York-City-FC-Atlanta-United-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/eee99db7/FC-Cincinnati-New-York-Red-Bulls-April-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f80d3365/New-England-Revolution-Charlotte-FC-April-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/cd79ef4e/Sporting-Kansas-City-Portland-Timbers-April-7-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c1a70efa/Minnesota-United-Real-Salt-Lake-April-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/603e6328/Seattle-Sounders-CF-Montreal-April-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c03fbc1a/Austin-FC-San-Jose-Earthquakes-April-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2d9f0d72/Nashville-SC-Philadelphia-Union-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3b5e1657/Chicago-Fire-Houston-Dynamo-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/603e6328/Seattle-Sounders-FC-CF-Montreal-April-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c03fbc1a/Austin-FC-San-Jose-Earthquakes-April-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c1a70efa/Minnesota-United-Real-Salt-Lake-April-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/cb095ec9/St-Louis-City-FC-Dallas-April-6-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/811d5ac7/Portland-Timbers-Los-Angeles-FC-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/45ec3a57/New-York-Red-Bulls-Chicago-Fire-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0a5d01ce/CF-Montreal-FC-Cincinnati-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a5134bd7/DC-United-Orlando-City-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/34d70769/New-York-City-FC-New-England-Revolution-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/45ec3a57/New-York-Red-Bulls-Chicago-Fire-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/89649673/Charlotte-FC-Toronto-FC-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a5134bd7/DC-United-Orlando-City-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c039eaaf/Atlanta-United-Philadelphia-Union-April-14-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/421c5841/St-Louis-City-Austin-FC-April-14-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/34f6b2f2/Vancouver-Whitecaps-FC-LA-Galaxy-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/315d0d90/FC-Dallas-Seattle-Sounders-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5aadf378/San-Jose-Earthquakes-Colorado-Rapids-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9800a9d3/Minnesota-United-Houston-Dynamo-April-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/214b3f4d/Real-Salt-Lake-Columbus-Crew-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/315d0d90/FC-Dallas-Seattle-Sounders-FC-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/34f6b2f2/Vancouver-Whitecaps-FC-LA-Galaxy-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5aadf378/San-Jose-Earthquakes-Colorado-Rapids-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6b527863/Sporting-Kansas-City-Inter-Miami-April-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9800a9d3/Minnesota-United-Houston-Dynamo-April-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3a1b56cb/Atlanta-United-FC-Cincinnati-April-20-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ca5b6986/Inter-Miami-Nashville-SC-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/75fde75d/Columbus-Crew-Portland-Timbers-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ba3f4e39/Toronto-FC-New-England-Revolution-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4db3074c/CF-Montreal-Orlando-City-April-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/75fde75d/Columbus-Crew-Portland-Timbers-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/90a1eb63/New-York-City-FC-DC-United-April-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ba3f4e39/Toronto-FC-New-England-Revolution-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ca5b6986/Inter-Miami-Nashville-SC-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/03cccbbc/Charlotte-FC-Minnesota-United-April-21-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bb9c1d23/Los-Angeles-FC-New-York-Red-Bulls-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/395bf6ef/Chicago-Fire-Real-Salt-Lake-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ba3c6c8c/Sporting-Kansas-City-St-Louis-City-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b5ef2e57/Seattle-Sounders-Vancouver-Whitecaps-FC-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aaaee2b6/Colorado-Rapids-FC-Dallas-April-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/244f80fc/Houston-Dynamo-Austin-FC-April-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/395bf6ef/Chicago-Fire-Real-Salt-Lake-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/aaaee2b6/Colorado-Rapids-FC-Dallas-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b5ef2e57/Seattle-Sounders-FC-Vancouver-Whitecaps-FC-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ba3c6c8c/Sporting-Kansas-City-St-Louis-City-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bb9c1d23/Los-Angeles-FC-New-York-Red-Bulls-April-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/003a9b0a/California-Clasico-LA-Galaxy-San-Jose-Earthquakes-April-21-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9141b60b/Austin-FC-LA-Galaxy-April-27-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8f3eb7ad/New-York-Red-Bulls-Vancouver-Whitecaps-FC-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2e6ddd5a/Columbus-Crew-CF-Montreal-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6550a0e0/Philadelphia-Union-Real-Salt-Lake-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3d29306/New-England-Revolution-Inter-Miami-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/748dfdfe/New-York-City-FC-Charlotte-FC-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d9912658/DC-United-Seattle-Sounders-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e44efb09/Orlando-City-Toronto-FC-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/05b6ea1f/FC-Cincinnati-Colorado-Rapids-April-27-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2e6ddd5a/Columbus-Crew-CF-Montreal-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6550a0e0/Philadelphia-Union-Real-Salt-Lake-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/748dfdfe/New-York-City-FC-Charlotte-FC-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8f3eb7ad/New-York-Red-Bulls-Vancouver-Whitecaps-FC-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b3d29306/New-England-Revolution-Inter-Miami-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d9912658/DC-United-Seattle-Sounders-FC-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e44efb09/Orlando-City-Toronto-FC-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2cf27dc0/Chicago-Fire-Atlanta-United-April-27-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/628605a9/Minnesota-United-Sporting-Kansas-City-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f2fb4c0e/Nashville-SC-San-Jose-Earthquakes-April-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3ee3b03b/Los-Angeles-FC-Portland-Timbers-April-27-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3f64fa56/FC-Dallas-Houston-Dynamo-April-27-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/628605a9/Minnesota-United-Sporting-Kansas-City-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f2fb4c0e/Nashville-SC-San-Jose-Earthquakes-April-27-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5688e70e/Philadelphia-Union-Seattle-Sounders-FC-April-30-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/5688e70e/Philadelphia-Union-Seattle-Sounders-April-30-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/84ef8c0d/San-Jose-Earthquakes-Los-Angeles-FC-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/94440830/Toronto-FC-FC-Dallas-May-4-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/240e5c11/DC-United-Philadelphia-Union-May-4-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0e3dc607/Inter-Miami-New-York-Red-Bulls-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/240e5c11/DC-United-Philadelphia-Union-May-4-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2ce5d297/Charlotte-FC-Portland-Timbers-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e7276237/Atlanta-United-Minnesota-United-May-4-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/329c83ce/Orlando-City-FC-Cincinnati-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/94440830/Toronto-FC-FC-Dallas-May-4-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e7276237/Atlanta-United-Minnesota-United-May-4-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/916ef4c6/Seattle-Sounders-FC-LA-Galaxy-May-5-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/916ef4c6/Seattle-Sounders-LA-Galaxy-May-5-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/765e3ddc/New-York-City-FC-Colorado-Rapids-May-5-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/93b66735/Real-Salt-Lake-Sporting-Kansas-City-May-4-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1193e66a/Chicago-Fire-New-England-Revolution-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1e0ed80e/Vancouver-Whitecaps-FC-Austin-FC-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fab2c4ff/Nashville-SC-CF-Montreal-May-4-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/216fbb89/Houston-Dynamo-St-Louis-City-May-4-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/93b66735/Real-Salt-Lake-Sporting-Kansas-City-May-4-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fab2c4ff/Nashville-SC-CF-Montreal-May-4-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/54c12e73/Philadelphia-Union-Orlando-City-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8c0ef45a/New-York-Red-Bulls-New-England-Revolution-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/52c17cb6/Atlanta-United-DC-United-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5876b797/Toronto-FC-New-York-City-FC-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/58f6002a/CF-Montreal-Inter-Miami-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1e4e3f9a/Charlotte-FC-Nashville-SC-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/52c17cb6/Atlanta-United-DC-United-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/54c12e73/Philadelphia-Union-Orlando-City-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5876b797/Toronto-FC-New-York-City-FC-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/58f6002a/CF-Montreal-Inter-Miami-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8c0ef45a/New-York-Red-Bulls-New-England-Revolution-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/854d1831/Columbus-Crew-FC-Cincinnati-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/0fa55bea/Portland-Timbers-Seattle-Sounders-FC-May-12-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/0fa55bea/Portland-Timbers-Seattle-Sounders-May-12-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/25688118/LA-Galaxy-Real-Salt-Lake-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ef15515f/FC-Dallas-Austin-FC-May-11-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/97e0b3fe/Sporting-Kansas-City-Houston-Dynamo-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2372ac4b/St-Louis-City-Chicago-Fire-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/25688118/LA-Galaxy-Real-Salt-Lake-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/97e0b3fe/Sporting-Kansas-City-Houston-Dynamo-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e51a4cdc/Colorado-Rapids-San-Jose-Earthquakes-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ef15515f/FC-Dallas-Austin-FC-May-11-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f3136125/Los-Angeles-FC-Vancouver-Whitecaps-FC-May-11-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0df2e11a/FC-Cincinnati-Atlanta-United-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/968ef849/DC-United-New-York-Red-Bulls-May-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0e61b36b/Philadelphia-Union-New-York-City-FC-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4f10ca76/Orlando-City-Inter-Miami-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/968ef849/DC-United-New-York-Red-Bulls-May-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bfb6a07b/CF-Montreal-Columbus-Crew-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/22924e56/Austin-FC-Houston-Dynamo-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bdafd273/Minnesota-United-LA-Galaxy-May-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/89d0abe1/Real-Salt-Lake-Seattle-Sounders-May-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7c251e31/Chicago-Fire-Charlotte-FC-May-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2f8c4131/Portland-Timbers-San-Jose-Earthquakes-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bd015c13/Nashville-SC-Toronto-FC-May-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4a75db5f/Colorado-Rapids-Vancouver-Whitecaps-FC-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7c251e31/Chicago-Fire-Charlotte-FC-May-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/805de38b/St-Louis-City-Los-Angeles-FC-May-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/89d0abe1/Real-Salt-Lake-Seattle-Sounders-FC-May-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bd015c13/Nashville-SC-Toronto-FC-May-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bdafd273/Minnesota-United-LA-Galaxy-May-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2c68d504/Nashville-SC-Atlanta-United-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bace4be5/Charlotte-FC-LA-Galaxy-May-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/91fccbd6/New-York-City-FC-New-York-Red-Bulls-May-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/21bd8a8f/Toronto-FC-CF-Montreal-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/53879222/FC-Cincinnati-St-Louis-City-May-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/beb05982/New-England-Revolution-Philadelphia-Union-May-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3bb1970e/Inter-Miami-DC-United-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/53879222/FC-Cincinnati-St-Louis-City-May-18-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/91fccbd6/New-York-City-FC-New-York-Red-Bulls-May-18-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bace4be5/Charlotte-FC-LA-Galaxy-May-18-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/beb05982/New-England-Revolution-Philadelphia-Union-May-18-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/e976169a/Chicago-Fire-Columbus-Crew-May-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7a7dea1a/Real-Salt-Lake-Colorado-Rapids-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/52f6b357/San-Jose-Earthquakes-Orlando-City-May-18-2024-Major-League-Soccer</t>
@@ -1769,312 +2159,306 @@
     <t>https://fbref.com/en/matches/535579d8/Austin-FC-Sporting-Kansas-City-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/58a45d6b/Seattle-Sounders-FC-Vancouver-Whitecaps-FC-May-18-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/b746d39e/Minnesota-United-Portland-Timbers-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/658978b8/Houston-Dynamo-FC-Dallas-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7a7dea1a/Real-Salt-Lake-Colorado-Rapids-May-18-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b746d39e/Minnesota-United-Portland-Timbers-May-18-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e976169a/Chicago-Fire-Columbus-Crew-May-18-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/58a45d6b/Seattle-Sounders-Vancouver-Whitecaps-FC-May-18-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/198ee8fc/CF-Montreal-Nashville-SC-May-25-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/33f1f77a/Charlotte-FC-Philadelphia-Union-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ef1106c2/New-England-Revolution-New-York-City-FC-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f43c6fe8/Orlando-City-Columbus-Crew-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/679258d6/Toronto-FC-FC-Cincinnati-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/eea0cd00/Atlanta-United-Los-Angeles-FC-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/30542b1b/DC-United-Chicago-Fire-May-25-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/33f1f77a/Charlotte-FC-Philadelphia-Union-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/679258d6/Toronto-FC-FC-Cincinnati-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/eea0cd00/Atlanta-United-Los-Angeles-FC-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ef1106c2/New-England-Revolution-New-York-City-FC-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f43c6fe8/Orlando-City-Columbus-Crew-May-25-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/50a966c2/Colorado-Rapids-Minnesota-United-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd6a5705/LA-Galaxy-Houston-Dynamo-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3609bf32/Portland-Timbers-Sporting-Kansas-City-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9bbbfca2/San-Jose-Earthquakes-Austin-FC-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ce6a9fbe/St-Louis-City-Seattle-Sounders-May-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b76f997a/Vancouver-Whitecaps-FC-Inter-Miami-May-25-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/022f73ae/FC-Dallas-Real-Salt-Lake-May-25-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3609bf32/Portland-Timbers-Sporting-Kansas-City-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/50a966c2/Colorado-Rapids-Minnesota-United-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9bbbfca2/San-Jose-Earthquakes-Austin-FC-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b76f997a/Vancouver-Whitecaps-FC-Inter-Miami-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce6a9fbe/St-Louis-City-Seattle-Sounders-FC-May-25-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fd6a5705/LA-Galaxy-Houston-Dynamo-May-25-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/5669fd57/New-York-Red-Bulls-Charlotte-FC-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b19c2ffc/Inter-Miami-Atlanta-United-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6016a41a/FC-Cincinnati-Nashville-SC-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/17a36202/CF-Montreal-DC-United-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5669fd57/New-York-Red-Bulls-Charlotte-FC-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6016a41a/FC-Cincinnati-Nashville-SC-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6f099543/Philadelphia-Union-Toronto-FC-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b19c2ffc/Inter-Miami-Atlanta-United-May-29-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/bbaf48cb/Sporting-Kansas-City-Vancouver-Whitecaps-FC-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f92a7948/Chicago-Fire-Orlando-City-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/abdec1e1/Austin-FC-Portland-Timbers-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/93a3b656/Houston-Dynamo-Colorado-Rapids-May-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/82ca4d08/Seattle-Sounders-Real-Salt-Lake-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/04c56680/LA-Galaxy-FC-Dallas-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/82ca4d08/Seattle-Sounders-FC-Real-Salt-Lake-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/93a3b656/Houston-Dynamo-Colorado-Rapids-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/abdec1e1/Austin-FC-Portland-Timbers-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bbaf48cb/Sporting-Kansas-City-Vancouver-Whitecaps-FC-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f92a7948/Chicago-Fire-Orlando-City-May-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/973f1dbc/Los-Angeles-FC-Minnesota-United-May-29-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b98f0356/New-York-City-FC-San-Jose-Earthquakes-May-31-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/eb5fb03e/Inter-Miami-St-Louis-City-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6c9704fa/Philadelphia-Union-CF-Montreal-June-1-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e2ae1793/DC-United-Toronto-FC-June-1-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/eb5fb03e/Inter-Miami-St-Louis-City-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ed7bcef7/New-York-Red-Bulls-Orlando-City-June-1-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1e81834c/Atlanta-United-Charlotte-FC-June-2-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4e312ea7/Real-Salt-Lake-Austin-FC-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/628fc15b/Chicago-Fire-LA-Galaxy-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5cbf9829/Minnesota-United-Sporting-Kansas-City-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d7401fe4/Vancouver-Whitecaps-FC-Colorado-Rapids-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca9d6065/Nashville-SC-New-England-Revolution-June-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/10e07cd8/Los-Angeles-FC-FC-Dallas-June-1-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4e312ea7/Real-Salt-Lake-Austin-FC-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5cbf9829/Minnesota-United-Sporting-Kansas-City-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/628fc15b/Chicago-Fire-LA-Galaxy-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c9e0e6df/Portland-Timbers-Houston-Dynamo-June-1-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ca9d6065/Nashville-SC-New-England-Revolution-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d7401fe4/Vancouver-Whitecaps-FC-Colorado-Rapids-June-1-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6ef8bb0d/New-England-Revolution-New-York-Red-Bulls-June-8-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/671bb1b0/St-Louis-City-Portland-Timbers-June-8-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/749a3352/Sporting-Kansas-City-Seattle-Sounders-June-8-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/611051e1/Minnesota-United-FC-Dallas-June-8-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/671bb1b0/St-Louis-City-Portland-Timbers-June-8-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/749a3352/Sporting-Kansas-City-Seattle-Sounders-FC-June-8-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/10a41ebe/Orlando-City-Los-Angeles-FC-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9cc0529a/Philadelphia-Union-Inter-Miami-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0af6242a/CF-Montreal-Real-Salt-Lake-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/10a41ebe/Orlando-City-Los-Angeles-FC-June-15-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/8e445374/Atlanta-United-Houston-Dynamo-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2d7ffe2/Charlotte-FC-DC-United-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/519eb9c3/New-England-Revolution-Vancouver-Whitecaps-FC-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d3e2ccc1/Toronto-FC-Chicago-Fire-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/59694344/New-York-Red-Bulls-Nashville-SC-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8e445374/Atlanta-United-Houston-Dynamo-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9cc0529a/Philadelphia-Union-Inter-Miami-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b2d7ffe2/Charlotte-FC-DC-United-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d3e2ccc1/Toronto-FC-Chicago-Fire-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b257fd16/New-York-City-FC-Columbus-Crew-June-14-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b1a9a845/Seattle-Sounders-Minnesota-United-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f3c4e115/San-Jose-Earthquakes-FC-Cincinnati-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/518f8d53/FC-Dallas-St-Louis-City-June-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/083ebbce/LA-Galaxy-Sporting-Kansas-City-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/518f8d53/FC-Dallas-St-Louis-City-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a79d94b1/Colorado-Rapids-Austin-FC-June-15-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b1a9a845/Seattle-Sounders-FC-Minnesota-United-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f3c4e115/San-Jose-Earthquakes-FC-Cincinnati-June-15-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2b3b7b51/Inter-Miami-Columbus-Crew-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/64daa8d8/Toronto-FC-Nashville-SC-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fd7fd486/DC-United-Atlanta-United-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ee7b834d/Charlotte-FC-Orlando-City-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/f91383d4/CF-Montreal-New-York-Red-Bulls-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fd7fd486/DC-United-Atlanta-United-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/be05b176/FC-Cincinnati-Philadelphia-Union-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8a76bacd/Houston-Dynamo-Seattle-Sounders-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd2e9aa9/Sporting-Kansas-City-Real-Salt-Lake-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/855e2336/San-Jose-Earthquakes-Portland-Timbers-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ab514d47/St-Louis-City-Colorado-Rapids-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/56e8cca3/Austin-FC-Los-Angeles-FC-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d04dbf8d/FC-Dallas-Minnesota-United-June-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/470c300c/LA-Galaxy-New-York-City-FC-June-19-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/56e8cca3/Austin-FC-Los-Angeles-FC-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/855e2336/San-Jose-Earthquakes-Portland-Timbers-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8a76bacd/Houston-Dynamo-Seattle-Sounders-FC-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ab514d47/St-Louis-City-Colorado-Rapids-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d04dbf8d/FC-Dallas-Minnesota-United-June-19-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fd2e9aa9/Sporting-Kansas-City-Real-Salt-Lake-June-19-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/84511c19/FC-Cincinnati-New-England-Revolution-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b0d4b5ba/Philadelphia-Union-Charlotte-FC-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6e5024ee/Columbus-Crew-Sporting-Kansas-City-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/63776ca0/DC-United-Houston-Dynamo-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/08da68e7/New-York-Red-Bulls-Toronto-FC-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/63776ca0/DC-United-Houston-Dynamo-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6e5024ee/Columbus-Crew-Sporting-Kansas-City-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/84511c19/FC-Cincinnati-New-England-Revolution-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b0d4b5ba/Philadelphia-Union-Charlotte-FC-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d11c358d/Orlando-City-Chicago-Fire-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9dbd8bc1/Nashville-SC-New-York-City-FC-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/97febfaa/Portland-Timbers-Vancouver-Whitecaps-FC-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8e7f6842/Colorado-Rapids-CF-Montreal-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c419d850/Minnesota-United-Austin-FC-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/25a3e9b8/St-Louis-City-Atlanta-United-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4cef16cb/Seattle-Sounders-FC-FC-Dallas-June-22-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/4cef16cb/Seattle-Sounders-FC-Dallas-June-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6b75e8c0/Los-Angeles-FC-San-Jose-Earthquakes-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/675d8558/Real-Salt-Lake-LA-Galaxy-June-22-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6b75e8c0/Los-Angeles-FC-San-Jose-Earthquakes-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8e7f6842/Colorado-Rapids-CF-Montreal-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/97febfaa/Portland-Timbers-Vancouver-Whitecaps-FC-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9dbd8bc1/Nashville-SC-New-York-City-FC-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c419d850/Minnesota-United-Austin-FC-June-22-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4b0b42f5/New-York-City-FC-Orlando-City-June-28-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/115a9ae4/Atlanta-United-Toronto-FC-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f0c85ac7/New-England-Revolution-Columbus-Crew-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/45280bcf/CF-Montreal-Philadelphia-Union-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/15593601/New-York-Red-Bulls-DC-United-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/45280bcf/CF-Montreal-Philadelphia-Union-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f0c85ac7/New-England-Revolution-Columbus-Crew-June-29-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/ce03db3e/Sporting-Kansas-City-Austin-FC-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d25b8ed4/California-Clasico-San-Jose-Earthquakes-LA-Galaxy-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bfc408d1/Portland-Timbers-Minnesota-United-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/96faaf3d/Seattle-Sounders-Chicago-Fire-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a5f4413f/Houston-Dynamo-Charlotte-FC-June-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/29cb3cc4/Nashville-SC-Inter-Miami-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/23594173/Los-Angeles-FC-Colorado-Rapids-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/29cb3cc4/Nashville-SC-Inter-Miami-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/82c20f2e/Vancouver-Whitecaps-FC-St-Louis-City-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/96faaf3d/Seattle-Sounders-FC-Chicago-Fire-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a5f4413f/Houston-Dynamo-Charlotte-FC-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bfc408d1/Portland-Timbers-Minnesota-United-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce03db3e/Sporting-Kansas-City-Austin-FC-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d25b8ed4/California-Clasico-San-Jose-Earthquakes-LA-Galaxy-June-29-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/dc85f8b9/FC-Dallas-FC-Cincinnati-June-29-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -2096,15 +2480,15 @@
     <t>https://fbref.com/en/matches/0324e353/Chicago-Fire-Philadelphia-Union-July-3-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d1efe5b4/Real-Salt-Lake-Houston-Dynamo-July-3-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca39c1ab/St-Louis-City-San-Jose-Earthquakes-July-3-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3f94d9e8/Minnesota-United-Vancouver-Whitecaps-FC-July-3-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ca39c1ab/St-Louis-City-San-Jose-Earthquakes-July-3-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d1efe5b4/Real-Salt-Lake-Houston-Dynamo-July-3-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3f6abc7c/Columbus-Crew-Nashville-SC-July-3-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -2117,22 +2501,22 @@
     <t>https://fbref.com/en/matches/0f24e61f/El-Trafico-LA-Galaxy-Los-Angeles-FC-July-4-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d6dfedd9/CF-Montreal-Vancouver-Whitecaps-FC-July-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c9508ef2/Columbus-Crew-Toronto-FC-July-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/93dc3067/FC-Cincinnati-Inter-Miami-July-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8ffa5713/Orlando-City-DC-United-July-6-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/93dc3067/FC-Cincinnati-Inter-Miami-July-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c9508ef2/Columbus-Crew-Toronto-FC-July-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d6dfedd9/CF-Montreal-Vancouver-Whitecaps-FC-July-6-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/dd691a72/Philadelphia-Union-New-York-Red-Bulls-July-6-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/72bc2e56/Seattle-Sounders-FC-New-England-Revolution-July-6-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/72bc2e56/Seattle-Sounders-New-England-Revolution-July-6-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d3d791b4/Real-Salt-Lake-Atlanta-United-July-6-2024-Major-League-Soccer</t>
@@ -2147,27 +2531,27 @@
     <t>https://fbref.com/en/matches/04d1f89e/Sporting-Kansas-City-FC-Dallas-July-7-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6008e564/LA-Galaxy-Minnesota-United-July-7-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/51827950/Portland-Timbers-Nashville-SC-July-7-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/17b212c1/Colorado-Rapids-St-Louis-City-July-7-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/51827950/Portland-Timbers-Nashville-SC-July-7-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6008e564/LA-Galaxy-Minnesota-United-July-7-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/ab9eac8f/FC-Cincinnati-Charlotte-FC-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/27a7f49f/Toronto-FC-Philadelphia-Union-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/99ce6c56/DC-United-Nashville-SC-July-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6615b63b/New-England-Revolution-Orlando-City-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/99ce6c56/DC-United-Nashville-SC-July-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ab9eac8f/FC-Cincinnati-Charlotte-FC-July-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/faa718d1/CF-Montreal-Atlanta-United-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -2177,10 +2561,13 @@
     <t>https://fbref.com/en/matches/43e4e2ad/San-Jose-Earthquakes-Sporting-Kansas-City-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4bc68976/FC-Dallas-LA-Galaxy-July-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/493e8795/Los-Angeles-FC-Columbus-Crew-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4bc68976/FC-Dallas-LA-Galaxy-July-13-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/fcbd4ca6/Austin-FC-Seattle-Sounders-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7c37f917/Chicago-Fire-New-York-City-FC-July-13-2024-Major-League-Soccer</t>
@@ -2192,9 +2579,6 @@
     <t>https://fbref.com/en/matches/ab60fec8/Colorado-Rapids-New-York-Red-Bulls-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fcbd4ca6/Austin-FC-Seattle-Sounders-FC-July-13-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/664cf277/Houston-Dynamo-Minnesota-United-July-13-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -2204,126 +2588,132 @@
     <t>https://fbref.com/en/matches/60f17870/Philadelphia-Union-New-England-Revolution-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e9eb6b8b/Inter-Miami-Toronto-FC-July-17-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b4944b94/Columbus-Crew-Charlotte-FC-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f4964b7c/FC-Cincinnati-Chicago-Fire-July-17-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b5f24684/New-York-Red-Bulls-CF-Montreal-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e9eb6b8b/Inter-Miami-Toronto-FC-July-17-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f4964b7c/FC-Cincinnati-Chicago-Fire-July-17-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3755ad8a/Seattle-Sounders-FC-St-Louis-City-July-17-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/3755ad8a/Seattle-Sounders-St-Louis-City-July-17-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd6a2d43/San-Jose-Earthquakes-Houston-Dynamo-July-17-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e2bbd69d/Minnesota-United-DC-United-July-17-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6a53bdca/Vancouver-Whitecaps-FC-Sporting-Kansas-City-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4ab1add3/Nashville-SC-Orlando-City-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6a53bdca/Vancouver-Whitecaps-FC-Sporting-Kansas-City-July-17-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/f10780b4/LA-Galaxy-Colorado-Rapids-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/cb449b4c/FC-Dallas-Austin-FC-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e2bbd69d/Minnesota-United-DC-United-July-17-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f10780b4/LA-Galaxy-Colorado-Rapids-July-17-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fd6a2d43/San-Jose-Earthquakes-Houston-Dynamo-July-17-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c7b119b8/Los-Angeles-FC-Real-Salt-Lake-July-17-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6745eb76/Philadelphia-Union-Nashville-SC-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0b92d25c/Inter-Miami-Chicago-Fire-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6745eb76/Philadelphia-Union-Nashville-SC-July-20-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/e9c95c54/Atlanta-United-Columbus-Crew-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/af5d68bd/New-England-Revolution-FC-Dallas-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d22e2ea6/New-York-Red-Bulls-FC-Cincinnati-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dc671d08/Orlando-City-New-York-City-FC-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c6c47bd5/CF-Montreal-Toronto-FC-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d22e2ea6/New-York-Red-Bulls-FC-Cincinnati-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/dc671d08/Orlando-City-New-York-City-FC-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e9c95c54/Atlanta-United-Columbus-Crew-July-20-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/43d2d102/Vancouver-Whitecaps-FC-Houston-Dynamo-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c065ff91/Colorado-Rapids-Real-Salt-Lake-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3479c662/Sporting-Kansas-City-St-Louis-City-July-20-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ce8fd7d6/Seattle-Sounders-Los-Angeles-FC-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1860ab70/Austin-FC-Charlotte-FC-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3479c662/Sporting-Kansas-City-St-Louis-City-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/43d2d102/Vancouver-Whitecaps-FC-Houston-Dynamo-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/67f48250/Minnesota-United-San-Jose-Earthquakes-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c065ff91/Colorado-Rapids-Real-Salt-Lake-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce8fd7d6/Seattle-Sounders-FC-Los-Angeles-FC-July-20-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f6e88d1c/LA-Galaxy-Portland-Timbers-July-20-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e5be22d7/Minnesota-United-Seattle-Sounders-FC-August-24-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/e5be22d7/Minnesota-United-Seattle-Sounders-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/00e2206c/New-York-City-FC-Chicago-Fire-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f82480f6/Charlotte-FC-New-York-Red-Bulls-August-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/46878a80/Inter-Miami-FC-Cincinnati-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/acc84c90/DC-United-FC-Dallas-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f82480f6/Charlotte-FC-New-York-Red-Bulls-August-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fc1099f0/CF-Montreal-New-England-Revolution-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/85dc8761/Portland-Timbers-St-Louis-City-August-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8c7d3a43/Nashville-SC-Austin-FC-August-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4d34c7cf/Real-Salt-Lake-San-Jose-Earthquakes-August-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/305def97/Sporting-Kansas-City-Orlando-City-August-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/235f179c/LA-Galaxy-Atlanta-United-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/305def97/Sporting-Kansas-City-Orlando-City-August-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4d34c7cf/Real-Salt-Lake-San-Jose-Earthquakes-August-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/85dc8761/Portland-Timbers-St-Louis-City-August-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8c7d3a43/Nashville-SC-Austin-FC-August-24-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b9f589d4/Houston-Dynamo-Toronto-FC-August-24-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/8c446928/Philadelphia-Union-Columbus-Crew-August-28-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9dcf6b5c/New-York-Red-Bulls-Philadelphia-Union-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/035907cf/Toronto-FC-DC-United-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c0cd18b9/Charlotte-FC-Atlanta-United-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6b085b5a/Orlando-City-Nashville-SC-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
@@ -2333,37 +2723,31 @@
     <t>https://fbref.com/en/matches/763be4b7/FC-Cincinnati-CF-Montreal-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9dcf6b5c/New-York-Red-Bulls-Philadelphia-Union-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c0cd18b9/Charlotte-FC-Atlanta-United-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/64d5c015/St-Louis-City-LA-Galaxy-September-1-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/01224e17/Portland-Timbers-Seattle-Sounders-FC-August-31-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/01224e17/Portland-Timbers-Seattle-Sounders-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4021beb0/Chicago-Fire-Inter-Miami-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0275bc70/Los-Angeles-FC-Houston-Dynamo-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/df8c77c3/Real-Salt-Lake-New-England-Revolution-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8e90b77b/San-Jose-Earthquakes-Minnesota-United-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/573d7d4b/Austin-FC-Vancouver-Whitecaps-FC-August-31-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/330726c3/FC-Dallas-Colorado-Rapids-August-31-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4021beb0/Chicago-Fire-Inter-Miami-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/573d7d4b/Austin-FC-Vancouver-Whitecaps-FC-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8e90b77b/San-Jose-Earthquakes-Minnesota-United-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/df8c77c3/Real-Salt-Lake-New-England-Revolution-August-31-2024-Major-League-Soccer</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/09dabec5/Columbus-Crew-Seattle-Sounders-FC-September-7-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/09dabec5/Columbus-Crew-Seattle-Sounders-September-7-2024-Major-League-Soccer</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/da562cb2/New-York-Red-Bulls-Sporting-Kansas-City-September-7-2024-Major-League-Soccer</t>
@@ -2375,10 +2759,394 @@
     <t>https://fbref.com/en/matches/6a574629/Houston-Dynamo-Los-Angeles-FC-September-7-2024-Major-League-Soccer</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a6036159/Chicago-Fire-DC-United-September-7-2024-Major-League-Soccer</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6e65be1f/Vancouver-Whitecaps-FC-FC-Dallas-September-7-2024-Major-League-Soccer</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a6036159/Chicago-Fire-DC-United-September-7-2024-Major-League-Soccer</t>
+    <t>https://fbref.com/en/matches/ffb3c4ec/Orlando-City-New-England-Revolution-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f6ee0cae/Toronto-FC-Austin-FC-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/00a6c938/DC-United-New-York-City-FC-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c3fe48e7/CF-Montreal-Charlotte-FC-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9f5b80d7/FC-Cincinnati-Columbus-Crew-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9b54f115/Inter-Miami-Philadelphia-Union-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4dd80729/Atlanta-United-Nashville-SC-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a5937963/Seattle-Sounders-Sporting-Kansas-City-September-15-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3e99752/Vancouver-Whitecaps-FC-San-Jose-Earthquakes-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e0a8e36f/Houston-Dynamo-Real-Salt-Lake-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7d556c1d/St-Louis-City-Minnesota-United-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/755ea9f5/Chicago-Fire-New-York-Red-Bulls-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e7b27721/El-Trafico-LA-Galaxy-Los-Angeles-FC-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e938a91e/Colorado-Rapids-Portland-Timbers-September-14-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/785b7627/New-England-Revolution-CF-Montreal-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ae626038/Atlanta-United-Inter-Miami-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d35b397d/Toronto-FC-Columbus-Crew-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/05c5af5a/New-York-City-FC-Philadelphia-Union-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7a6a8af1/Los-Angeles-FC-Austin-FC-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c910714a/Houston-Dynamo-Vancouver-Whitecaps-FC-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5ccf3153/Nashville-SC-Chicago-Fire-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/833399a2/Sporting-Kansas-City-Colorado-Rapids-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/470ce725/Portland-Timbers-LA-Galaxy-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4263fc6f/Seattle-Sounders-San-Jose-Earthquakes-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/33e7a1b2/Real-Salt-Lake-FC-Dallas-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/21723188/Minnesota-United-FC-Cincinnati-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d3dd9a7a/Orlando-City-Charlotte-FC-September-18-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6cd36798/New-York-City-FC-Inter-Miami-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/652c14fe/Charlotte-FC-New-England-Revolution-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0662e8b6/CF-Montreal-Chicago-Fire-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/359bb7e0/Columbus-Crew-Orlando-City-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1fdb1022/New-York-Red-Bulls-Atlanta-United-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b87f98a6/Philadelphia-Union-DC-United-September-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f720f826/Nashville-SC-FC-Cincinnati-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6fb6e1cd/Sporting-Kansas-City-Minnesota-United-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b20da987/Real-Salt-Lake-Portland-Timbers-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3c25e753/FC-Dallas-Los-Angeles-FC-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ecfeaf11/LA-Galaxy-Vancouver-Whitecaps-FC-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ee19047b/San-Jose-Earthquakes-St-Louis-City-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/210ae64d/Austin-FC-Houston-Dynamo-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1c8ca7e3/Colorado-Rapids-Toronto-FC-September-21-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5d2f9027/CF-Montreal-San-Jose-Earthquakes-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ecb8c17f/Philadelphia-Union-Atlanta-United-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/51757f95/New-England-Revolution-Nashville-SC-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e485f11a/Inter-Miami-Charlotte-FC-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/97c55254/FC-Cincinnati-Los-Angeles-FC-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f3d5ad0a/New-York-Red-Bulls-New-York-City-FC-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f56f396c/DC-United-Columbus-Crew-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1995750e/Austin-FC-Real-Salt-Lake-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2a7d19cd/FC-Dallas-Orlando-City-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a6901c2a/Vancouver-Whitecaps-FC-Portland-Timbers-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9c216e1a/St-Louis-City-Sporting-Kansas-City-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2831aee/Seattle-Sounders-Houston-Dynamo-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e261efdd/Chicago-Fire-Toronto-FC-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e5e58676/Minnesota-United-Colorado-Rapids-September-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9ccf0f49/Charlotte-FC-Chicago-Fire-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9001ebb8/New-York-City-FC-FC-Cincinnati-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0f59c76f/Atlanta-United-CF-Montreal-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/67a9fdf2/Orlando-City-Philadelphia-Union-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6a9ca2c9/Toronto-FC-New-York-Red-Bulls-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/459f4ed3/Columbus-Crew-Inter-Miami-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/43204aae/Colorado-Rapids-LA-Galaxy-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/34cde001/Nashville-SC-DC-United-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/21f465a3/San-Jose-Earthquakes-FC-Dallas-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7b86f1be/Portland-Timbers-Austin-FC-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/41c92783/Real-Salt-Lake-Minnesota-United-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d80b24eb/Vancouver-Whitecaps-FC-Seattle-Sounders-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/217b7bc9/Houston-Dynamo-New-England-Revolution-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca65b4a2/Los-Angeles-FC-St-Louis-City-October-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c4b0c79a/Toronto-FC-Inter-Miami-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d99ff545/Vancouver-Whitecaps-FC-Minnesota-United-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/abcd6d46/New-England-Revolution-DC-United-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d299c4ba/Columbus-Crew-Philadelphia-Union-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/de9de963/FC-Cincinnati-Orlando-City-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ab19a9f3/Atlanta-United-New-York-Red-Bulls-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/763bce3f/Charlotte-FC-CF-Montreal-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3cb2213/Portland-Timbers-FC-Dallas-October-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0290de2f/New-York-City-FC-Nashville-SC-October-6-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f649f950/LA-Galaxy-Austin-FC-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aeda5992/Colorado-Rapids-Seattle-Sounders-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bdaab9f7/San-Jose-Earthquakes-Real-Salt-Lake-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b900c937/St-Louis-City-Houston-Dynamo-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a2be7ffc/Sporting-Kansas-City-Los-Angeles-FC-October-5-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2ce4d6c4/Columbus-Crew-New-England-Revolution-October-12-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d67b849b/Vancouver-Whitecaps-FC-Los-Angeles-FC-October-13-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b271451/Chicago-Fire-Nashville-SC-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/14bae930/New-York-Red-Bulls-Columbus-Crew-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/185d101d/CF-Montreal-New-York-City-FC-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/25cfb7b3/Philadelphia-Union-FC-Cincinnati-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1d8afe9a/Inter-Miami-New-England-Revolution-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c0f9b3cd/DC-United-Charlotte-FC-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d827dfa7/Orlando-City-Atlanta-United-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/81683c00/Seattle-Sounders-Portland-Timbers-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/efbae2b7/Los-Angeles-FC-San-Jose-Earthquakes-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d25b6770/Real-Salt-Lake-Vancouver-Whitecaps-FC-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/049c5ae9/FC-Dallas-Sporting-Kansas-City-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8689be76/Austin-FC-Colorado-Rapids-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/133a8f09/Minnesota-United-St-Louis-City-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1485ab6d/Houston-Dynamo-LA-Galaxy-October-19-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3b2862e8/CF-Montreal-Atlanta-United-October-22-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/acfa25fb/Vancouver-Whitecaps-FC-Portland-Timbers-October-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9828303d/Inter-Miami-Atlanta-United-October-25-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cbc07dec/Orlando-City-Charlotte-FC-October-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c8287886/LA-Galaxy-Colorado-Rapids-October-26-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92332590/Los-Angeles-FC-Vancouver-Whitecaps-FC-October-27-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6cb7c830/FC-Cincinnati-New-York-City-FC-October-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/724779c8/Seattle-Sounders-Houston-Dynamo-October-28-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/899277ad/Columbus-Crew-New-York-Red-Bulls-October-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/768df149/Real-Salt-Lake-Minnesota-United-October-29-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/367db979/Charlotte-FC-Orlando-City-November-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/319fec55/New-York-City-FC-FC-Cincinnati-November-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f214b6b0/Atlanta-United-Inter-Miami-November-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca615a4f/Colorado-Rapids-LA-Galaxy-November-1-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7d7e2ffc/New-York-Red-Bulls-Columbus-Crew-November-3-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ebd78237/Houston-Dynamo-Seattle-Sounders-November-3-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3e2d4a20/Minnesota-United-Real-Salt-Lake-November-2-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9e726acf/Vancouver-Whitecaps-FC-Los-Angeles-FC-November-3-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0761b1cf/FC-Cincinnati-New-York-City-FC-November-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b0ad266/Orlando-City-Charlotte-FC-November-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/be9f2b77/Los-Angeles-FC-Vancouver-Whitecaps-FC-November-8-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5c5b1c24/Inter-Miami-Atlanta-United-November-9-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7779d63d/New-York-City-FC-New-York-Red-Bulls-November-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/37d92c84/LA-Galaxy-Minnesota-United-November-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1b1e9591/Orlando-City-Atlanta-United-November-24-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3083b817/Los-Angeles-FC-Seattle-Sounders-November-23-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8474018b/LA-Galaxy-Seattle-Sounders-November-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/99eac7a3/Orlando-City-New-York-Red-Bulls-November-30-2024-Major-League-Soccer</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/77faff0a/LA-Galaxy-New-York-Red-Bulls-December-7-2024-Major-League-Soccer</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>395</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
@@ -2445,7 +3213,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>396</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4">
@@ -2453,7 +3221,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>397</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5">
@@ -2461,7 +3229,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>398</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6">
@@ -2469,7 +3237,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>399</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7">
@@ -2477,7 +3245,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -2485,7 +3253,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9">
@@ -2493,7 +3261,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>402</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10">
@@ -2501,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11">
@@ -2509,7 +3277,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12">
@@ -2517,7 +3285,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>405</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13">
@@ -2525,7 +3293,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>406</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14">
@@ -2533,7 +3301,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>407</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15">
@@ -2541,7 +3309,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>408</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16">
@@ -2549,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>537</v>
       </c>
     </row>
     <row r="17">
@@ -2557,7 +3325,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>410</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +3333,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19">
@@ -2573,7 +3341,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>412</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20">
@@ -2581,7 +3349,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>413</v>
+        <v>541</v>
       </c>
     </row>
     <row r="21">
@@ -2589,7 +3357,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>414</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22">
@@ -2597,7 +3365,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>415</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23">
@@ -2605,7 +3373,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>416</v>
+        <v>544</v>
       </c>
     </row>
     <row r="24">
@@ -2613,7 +3381,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>417</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25">
@@ -2621,7 +3389,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>418</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26">
@@ -2629,7 +3397,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>419</v>
+        <v>547</v>
       </c>
     </row>
     <row r="27">
@@ -2637,7 +3405,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>420</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28">
@@ -2645,7 +3413,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>421</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29">
@@ -2653,7 +3421,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>422</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30">
@@ -2661,7 +3429,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>551</v>
       </c>
     </row>
     <row r="31">
@@ -2669,7 +3437,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>424</v>
+        <v>552</v>
       </c>
     </row>
     <row r="32">
@@ -2677,7 +3445,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>425</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33">
@@ -2685,7 +3453,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>426</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34">
@@ -2693,7 +3461,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>427</v>
+        <v>555</v>
       </c>
     </row>
     <row r="35">
@@ -2701,7 +3469,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>428</v>
+        <v>556</v>
       </c>
     </row>
     <row r="36">
@@ -2709,7 +3477,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>429</v>
+        <v>557</v>
       </c>
     </row>
     <row r="37">
@@ -2717,7 +3485,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>430</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38">
@@ -2725,7 +3493,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>431</v>
+        <v>559</v>
       </c>
     </row>
     <row r="39">
@@ -2733,7 +3501,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>432</v>
+        <v>560</v>
       </c>
     </row>
     <row r="40">
@@ -2741,7 +3509,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>433</v>
+        <v>561</v>
       </c>
     </row>
     <row r="41">
@@ -2749,7 +3517,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>434</v>
+        <v>562</v>
       </c>
     </row>
     <row r="42">
@@ -2757,7 +3525,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>435</v>
+        <v>563</v>
       </c>
     </row>
     <row r="43">
@@ -2765,7 +3533,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>436</v>
+        <v>564</v>
       </c>
     </row>
     <row r="44">
@@ -2773,7 +3541,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>437</v>
+        <v>565</v>
       </c>
     </row>
     <row r="45">
@@ -2781,7 +3549,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>438</v>
+        <v>566</v>
       </c>
     </row>
     <row r="46">
@@ -2789,7 +3557,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>439</v>
+        <v>567</v>
       </c>
     </row>
     <row r="47">
@@ -2797,7 +3565,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>440</v>
+        <v>568</v>
       </c>
     </row>
     <row r="48">
@@ -2805,7 +3573,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>441</v>
+        <v>569</v>
       </c>
     </row>
     <row r="49">
@@ -2813,7 +3581,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>442</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50">
@@ -2821,7 +3589,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>443</v>
+        <v>571</v>
       </c>
     </row>
     <row r="51">
@@ -2829,7 +3597,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>444</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52">
@@ -2837,7 +3605,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>445</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53">
@@ -2845,7 +3613,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>446</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54">
@@ -2853,7 +3621,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>447</v>
+        <v>575</v>
       </c>
     </row>
     <row r="55">
@@ -2861,7 +3629,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>448</v>
+        <v>576</v>
       </c>
     </row>
     <row r="56">
@@ -2869,7 +3637,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>449</v>
+        <v>577</v>
       </c>
     </row>
     <row r="57">
@@ -2877,7 +3645,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>450</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58">
@@ -2885,7 +3653,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>451</v>
+        <v>579</v>
       </c>
     </row>
     <row r="59">
@@ -2893,7 +3661,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>452</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +3669,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>453</v>
+        <v>581</v>
       </c>
     </row>
     <row r="61">
@@ -2909,7 +3677,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>454</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62">
@@ -2917,7 +3685,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>455</v>
+        <v>583</v>
       </c>
     </row>
     <row r="63">
@@ -2925,7 +3693,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>456</v>
+        <v>584</v>
       </c>
     </row>
     <row r="64">
@@ -2933,7 +3701,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>457</v>
+        <v>585</v>
       </c>
     </row>
     <row r="65">
@@ -2941,7 +3709,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>458</v>
+        <v>586</v>
       </c>
     </row>
     <row r="66">
@@ -2949,7 +3717,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>459</v>
+        <v>587</v>
       </c>
     </row>
     <row r="67">
@@ -2957,7 +3725,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>460</v>
+        <v>588</v>
       </c>
     </row>
     <row r="68">
@@ -2965,7 +3733,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>461</v>
+        <v>589</v>
       </c>
     </row>
     <row r="69">
@@ -2973,7 +3741,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>462</v>
+        <v>590</v>
       </c>
     </row>
     <row r="70">
@@ -2981,7 +3749,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>463</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71">
@@ -2989,7 +3757,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>464</v>
+        <v>592</v>
       </c>
     </row>
     <row r="72">
@@ -2997,7 +3765,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>465</v>
+        <v>593</v>
       </c>
     </row>
     <row r="73">
@@ -3005,7 +3773,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>466</v>
+        <v>594</v>
       </c>
     </row>
     <row r="74">
@@ -3013,7 +3781,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>467</v>
+        <v>595</v>
       </c>
     </row>
     <row r="75">
@@ -3021,7 +3789,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>468</v>
+        <v>596</v>
       </c>
     </row>
     <row r="76">
@@ -3029,7 +3797,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>469</v>
+        <v>597</v>
       </c>
     </row>
     <row r="77">
@@ -3037,7 +3805,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>470</v>
+        <v>598</v>
       </c>
     </row>
     <row r="78">
@@ -3045,7 +3813,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>471</v>
+        <v>599</v>
       </c>
     </row>
     <row r="79">
@@ -3053,7 +3821,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>472</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80">
@@ -3061,7 +3829,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>473</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81">
@@ -3069,7 +3837,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>474</v>
+        <v>602</v>
       </c>
     </row>
     <row r="82">
@@ -3077,7 +3845,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>475</v>
+        <v>603</v>
       </c>
     </row>
     <row r="83">
@@ -3085,7 +3853,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>476</v>
+        <v>604</v>
       </c>
     </row>
     <row r="84">
@@ -3093,7 +3861,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>477</v>
+        <v>605</v>
       </c>
     </row>
     <row r="85">
@@ -3101,7 +3869,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>478</v>
+        <v>606</v>
       </c>
     </row>
     <row r="86">
@@ -3109,7 +3877,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>479</v>
+        <v>607</v>
       </c>
     </row>
     <row r="87">
@@ -3117,7 +3885,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>480</v>
+        <v>608</v>
       </c>
     </row>
     <row r="88">
@@ -3125,7 +3893,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>481</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89">
@@ -3133,7 +3901,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>482</v>
+        <v>610</v>
       </c>
     </row>
     <row r="90">
@@ -3141,7 +3909,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>483</v>
+        <v>611</v>
       </c>
     </row>
     <row r="91">
@@ -3149,7 +3917,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>484</v>
+        <v>612</v>
       </c>
     </row>
     <row r="92">
@@ -3157,7 +3925,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>485</v>
+        <v>613</v>
       </c>
     </row>
     <row r="93">
@@ -3165,7 +3933,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>486</v>
+        <v>614</v>
       </c>
     </row>
     <row r="94">
@@ -3173,7 +3941,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>487</v>
+        <v>615</v>
       </c>
     </row>
     <row r="95">
@@ -3181,7 +3949,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>488</v>
+        <v>616</v>
       </c>
     </row>
     <row r="96">
@@ -3189,7 +3957,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>489</v>
+        <v>617</v>
       </c>
     </row>
     <row r="97">
@@ -3197,7 +3965,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>490</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98">
@@ -3205,7 +3973,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>491</v>
+        <v>619</v>
       </c>
     </row>
     <row r="99">
@@ -3213,7 +3981,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>492</v>
+        <v>620</v>
       </c>
     </row>
     <row r="100">
@@ -3221,7 +3989,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>493</v>
+        <v>621</v>
       </c>
     </row>
     <row r="101">
@@ -3229,7 +3997,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>494</v>
+        <v>622</v>
       </c>
     </row>
     <row r="102">
@@ -3237,7 +4005,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>495</v>
+        <v>623</v>
       </c>
     </row>
     <row r="103">
@@ -3245,7 +4013,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>496</v>
+        <v>624</v>
       </c>
     </row>
     <row r="104">
@@ -3253,7 +4021,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>497</v>
+        <v>625</v>
       </c>
     </row>
     <row r="105">
@@ -3261,7 +4029,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>498</v>
+        <v>626</v>
       </c>
     </row>
     <row r="106">
@@ -3269,7 +4037,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>499</v>
+        <v>627</v>
       </c>
     </row>
     <row r="107">
@@ -3277,7 +4045,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>500</v>
+        <v>628</v>
       </c>
     </row>
     <row r="108">
@@ -3285,7 +4053,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>501</v>
+        <v>629</v>
       </c>
     </row>
     <row r="109">
@@ -3293,7 +4061,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>502</v>
+        <v>630</v>
       </c>
     </row>
     <row r="110">
@@ -3301,7 +4069,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>503</v>
+        <v>631</v>
       </c>
     </row>
     <row r="111">
@@ -3309,7 +4077,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>504</v>
+        <v>632</v>
       </c>
     </row>
     <row r="112">
@@ -3317,7 +4085,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>505</v>
+        <v>633</v>
       </c>
     </row>
     <row r="113">
@@ -3325,7 +4093,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>506</v>
+        <v>634</v>
       </c>
     </row>
     <row r="114">
@@ -3333,7 +4101,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>507</v>
+        <v>635</v>
       </c>
     </row>
     <row r="115">
@@ -3341,7 +4109,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>508</v>
+        <v>636</v>
       </c>
     </row>
     <row r="116">
@@ -3349,7 +4117,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>509</v>
+        <v>637</v>
       </c>
     </row>
     <row r="117">
@@ -3357,7 +4125,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>510</v>
+        <v>638</v>
       </c>
     </row>
     <row r="118">
@@ -3365,7 +4133,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>511</v>
+        <v>639</v>
       </c>
     </row>
     <row r="119">
@@ -3373,7 +4141,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>512</v>
+        <v>640</v>
       </c>
     </row>
     <row r="120">
@@ -3381,7 +4149,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>513</v>
+        <v>641</v>
       </c>
     </row>
     <row r="121">
@@ -3389,7 +4157,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>514</v>
+        <v>642</v>
       </c>
     </row>
     <row r="122">
@@ -3397,7 +4165,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>515</v>
+        <v>643</v>
       </c>
     </row>
     <row r="123">
@@ -3405,7 +4173,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>516</v>
+        <v>644</v>
       </c>
     </row>
     <row r="124">
@@ -3413,7 +4181,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>517</v>
+        <v>645</v>
       </c>
     </row>
     <row r="125">
@@ -3421,7 +4189,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>518</v>
+        <v>646</v>
       </c>
     </row>
     <row r="126">
@@ -3429,7 +4197,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>519</v>
+        <v>647</v>
       </c>
     </row>
     <row r="127">
@@ -3437,7 +4205,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>520</v>
+        <v>648</v>
       </c>
     </row>
     <row r="128">
@@ -3445,7 +4213,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>521</v>
+        <v>649</v>
       </c>
     </row>
     <row r="129">
@@ -3453,7 +4221,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>522</v>
+        <v>650</v>
       </c>
     </row>
     <row r="130">
@@ -3461,7 +4229,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>523</v>
+        <v>651</v>
       </c>
     </row>
     <row r="131">
@@ -3469,7 +4237,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>524</v>
+        <v>652</v>
       </c>
     </row>
     <row r="132">
@@ -3477,7 +4245,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>525</v>
+        <v>653</v>
       </c>
     </row>
     <row r="133">
@@ -3485,7 +4253,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>526</v>
+        <v>654</v>
       </c>
     </row>
     <row r="134">
@@ -3493,7 +4261,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>527</v>
+        <v>655</v>
       </c>
     </row>
     <row r="135">
@@ -3501,7 +4269,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>528</v>
+        <v>656</v>
       </c>
     </row>
     <row r="136">
@@ -3509,7 +4277,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>529</v>
+        <v>657</v>
       </c>
     </row>
     <row r="137">
@@ -3517,7 +4285,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>530</v>
+        <v>658</v>
       </c>
     </row>
     <row r="138">
@@ -3525,7 +4293,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>531</v>
+        <v>659</v>
       </c>
     </row>
     <row r="139">
@@ -3533,7 +4301,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>532</v>
+        <v>660</v>
       </c>
     </row>
     <row r="140">
@@ -3541,7 +4309,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>533</v>
+        <v>661</v>
       </c>
     </row>
     <row r="141">
@@ -3549,7 +4317,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>534</v>
+        <v>662</v>
       </c>
     </row>
     <row r="142">
@@ -3557,7 +4325,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>535</v>
+        <v>663</v>
       </c>
     </row>
     <row r="143">
@@ -3565,7 +4333,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>536</v>
+        <v>664</v>
       </c>
     </row>
     <row r="144">
@@ -3573,7 +4341,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>537</v>
+        <v>665</v>
       </c>
     </row>
     <row r="145">
@@ -3581,7 +4349,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>538</v>
+        <v>666</v>
       </c>
     </row>
     <row r="146">
@@ -3589,7 +4357,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>539</v>
+        <v>667</v>
       </c>
     </row>
     <row r="147">
@@ -3597,7 +4365,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>540</v>
+        <v>668</v>
       </c>
     </row>
     <row r="148">
@@ -3605,7 +4373,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>541</v>
+        <v>669</v>
       </c>
     </row>
     <row r="149">
@@ -3613,7 +4381,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>542</v>
+        <v>670</v>
       </c>
     </row>
     <row r="150">
@@ -3621,7 +4389,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>543</v>
+        <v>671</v>
       </c>
     </row>
     <row r="151">
@@ -3629,7 +4397,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
     </row>
     <row r="152">
@@ -3637,7 +4405,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>545</v>
+        <v>673</v>
       </c>
     </row>
     <row r="153">
@@ -3645,7 +4413,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>546</v>
+        <v>674</v>
       </c>
     </row>
     <row r="154">
@@ -3653,7 +4421,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>547</v>
+        <v>675</v>
       </c>
     </row>
     <row r="155">
@@ -3661,7 +4429,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>548</v>
+        <v>676</v>
       </c>
     </row>
     <row r="156">
@@ -3669,7 +4437,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>549</v>
+        <v>677</v>
       </c>
     </row>
     <row r="157">
@@ -3677,7 +4445,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>550</v>
+        <v>678</v>
       </c>
     </row>
     <row r="158">
@@ -3685,7 +4453,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>551</v>
+        <v>679</v>
       </c>
     </row>
     <row r="159">
@@ -3693,7 +4461,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>552</v>
+        <v>680</v>
       </c>
     </row>
     <row r="160">
@@ -3701,7 +4469,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>553</v>
+        <v>681</v>
       </c>
     </row>
     <row r="161">
@@ -3709,7 +4477,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
     </row>
     <row r="162">
@@ -3717,7 +4485,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>555</v>
+        <v>683</v>
       </c>
     </row>
     <row r="163">
@@ -3725,7 +4493,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
     </row>
     <row r="164">
@@ -3733,7 +4501,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>557</v>
+        <v>685</v>
       </c>
     </row>
     <row r="165">
@@ -3741,7 +4509,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>558</v>
+        <v>686</v>
       </c>
     </row>
     <row r="166">
@@ -3749,7 +4517,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>559</v>
+        <v>687</v>
       </c>
     </row>
     <row r="167">
@@ -3757,7 +4525,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
     </row>
     <row r="168">
@@ -3765,7 +4533,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>561</v>
+        <v>689</v>
       </c>
     </row>
     <row r="169">
@@ -3773,7 +4541,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>562</v>
+        <v>690</v>
       </c>
     </row>
     <row r="170">
@@ -3781,7 +4549,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>563</v>
+        <v>691</v>
       </c>
     </row>
     <row r="171">
@@ -3789,7 +4557,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>564</v>
+        <v>692</v>
       </c>
     </row>
     <row r="172">
@@ -3797,7 +4565,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>565</v>
+        <v>693</v>
       </c>
     </row>
     <row r="173">
@@ -3805,7 +4573,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>566</v>
+        <v>694</v>
       </c>
     </row>
     <row r="174">
@@ -3813,7 +4581,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>567</v>
+        <v>695</v>
       </c>
     </row>
     <row r="175">
@@ -3821,7 +4589,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>568</v>
+        <v>696</v>
       </c>
     </row>
     <row r="176">
@@ -3829,7 +4597,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>569</v>
+        <v>697</v>
       </c>
     </row>
     <row r="177">
@@ -3837,7 +4605,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>570</v>
+        <v>698</v>
       </c>
     </row>
     <row r="178">
@@ -3845,7 +4613,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>571</v>
+        <v>699</v>
       </c>
     </row>
     <row r="179">
@@ -3853,7 +4621,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
     </row>
     <row r="180">
@@ -3861,7 +4629,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>573</v>
+        <v>701</v>
       </c>
     </row>
     <row r="181">
@@ -3869,7 +4637,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>574</v>
+        <v>702</v>
       </c>
     </row>
     <row r="182">
@@ -3877,7 +4645,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
     </row>
     <row r="183">
@@ -3885,7 +4653,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>576</v>
+        <v>704</v>
       </c>
     </row>
     <row r="184">
@@ -3893,7 +4661,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>577</v>
+        <v>705</v>
       </c>
     </row>
     <row r="185">
@@ -3901,7 +4669,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>578</v>
+        <v>706</v>
       </c>
     </row>
     <row r="186">
@@ -3909,7 +4677,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>579</v>
+        <v>707</v>
       </c>
     </row>
     <row r="187">
@@ -3917,7 +4685,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>580</v>
+        <v>708</v>
       </c>
     </row>
     <row r="188">
@@ -3925,7 +4693,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>581</v>
+        <v>709</v>
       </c>
     </row>
     <row r="189">
@@ -3933,7 +4701,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>582</v>
+        <v>710</v>
       </c>
     </row>
     <row r="190">
@@ -3941,7 +4709,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>583</v>
+        <v>711</v>
       </c>
     </row>
     <row r="191">
@@ -3949,7 +4717,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>584</v>
+        <v>712</v>
       </c>
     </row>
     <row r="192">
@@ -3957,7 +4725,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>585</v>
+        <v>713</v>
       </c>
     </row>
     <row r="193">
@@ -3965,7 +4733,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>586</v>
+        <v>714</v>
       </c>
     </row>
     <row r="194">
@@ -3973,7 +4741,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>587</v>
+        <v>715</v>
       </c>
     </row>
     <row r="195">
@@ -3981,7 +4749,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>588</v>
+        <v>716</v>
       </c>
     </row>
     <row r="196">
@@ -3989,7 +4757,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>589</v>
+        <v>717</v>
       </c>
     </row>
     <row r="197">
@@ -3997,7 +4765,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>590</v>
+        <v>718</v>
       </c>
     </row>
     <row r="198">
@@ -4005,7 +4773,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>591</v>
+        <v>719</v>
       </c>
     </row>
     <row r="199">
@@ -4013,7 +4781,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>592</v>
+        <v>720</v>
       </c>
     </row>
     <row r="200">
@@ -4021,7 +4789,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>593</v>
+        <v>721</v>
       </c>
     </row>
     <row r="201">
@@ -4029,7 +4797,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>594</v>
+        <v>722</v>
       </c>
     </row>
     <row r="202">
@@ -4037,7 +4805,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>595</v>
+        <v>723</v>
       </c>
     </row>
     <row r="203">
@@ -4045,7 +4813,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>596</v>
+        <v>724</v>
       </c>
     </row>
     <row r="204">
@@ -4053,7 +4821,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>597</v>
+        <v>725</v>
       </c>
     </row>
     <row r="205">
@@ -4061,7 +4829,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>598</v>
+        <v>726</v>
       </c>
     </row>
     <row r="206">
@@ -4069,7 +4837,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>599</v>
+        <v>727</v>
       </c>
     </row>
     <row r="207">
@@ -4077,7 +4845,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>600</v>
+        <v>728</v>
       </c>
     </row>
     <row r="208">
@@ -4085,7 +4853,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>601</v>
+        <v>729</v>
       </c>
     </row>
     <row r="209">
@@ -4093,7 +4861,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>602</v>
+        <v>730</v>
       </c>
     </row>
     <row r="210">
@@ -4101,7 +4869,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>603</v>
+        <v>731</v>
       </c>
     </row>
     <row r="211">
@@ -4109,7 +4877,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>604</v>
+        <v>732</v>
       </c>
     </row>
     <row r="212">
@@ -4117,7 +4885,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>605</v>
+        <v>733</v>
       </c>
     </row>
     <row r="213">
@@ -4125,7 +4893,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>606</v>
+        <v>734</v>
       </c>
     </row>
     <row r="214">
@@ -4133,7 +4901,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>607</v>
+        <v>735</v>
       </c>
     </row>
     <row r="215">
@@ -4141,7 +4909,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>608</v>
+        <v>736</v>
       </c>
     </row>
     <row r="216">
@@ -4149,7 +4917,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>609</v>
+        <v>737</v>
       </c>
     </row>
     <row r="217">
@@ -4157,7 +4925,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>610</v>
+        <v>738</v>
       </c>
     </row>
     <row r="218">
@@ -4165,7 +4933,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>611</v>
+        <v>739</v>
       </c>
     </row>
     <row r="219">
@@ -4173,7 +4941,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>612</v>
+        <v>740</v>
       </c>
     </row>
     <row r="220">
@@ -4181,7 +4949,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>613</v>
+        <v>741</v>
       </c>
     </row>
     <row r="221">
@@ -4189,7 +4957,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>614</v>
+        <v>742</v>
       </c>
     </row>
     <row r="222">
@@ -4197,7 +4965,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>615</v>
+        <v>743</v>
       </c>
     </row>
     <row r="223">
@@ -4205,7 +4973,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>616</v>
+        <v>744</v>
       </c>
     </row>
     <row r="224">
@@ -4213,7 +4981,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>617</v>
+        <v>745</v>
       </c>
     </row>
     <row r="225">
@@ -4221,7 +4989,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>618</v>
+        <v>746</v>
       </c>
     </row>
     <row r="226">
@@ -4229,7 +4997,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>619</v>
+        <v>747</v>
       </c>
     </row>
     <row r="227">
@@ -4237,7 +5005,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>620</v>
+        <v>748</v>
       </c>
     </row>
     <row r="228">
@@ -4245,7 +5013,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>621</v>
+        <v>749</v>
       </c>
     </row>
     <row r="229">
@@ -4253,7 +5021,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>622</v>
+        <v>750</v>
       </c>
     </row>
     <row r="230">
@@ -4261,7 +5029,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>623</v>
+        <v>751</v>
       </c>
     </row>
     <row r="231">
@@ -4269,7 +5037,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>624</v>
+        <v>752</v>
       </c>
     </row>
     <row r="232">
@@ -4277,7 +5045,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>625</v>
+        <v>753</v>
       </c>
     </row>
     <row r="233">
@@ -4285,7 +5053,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>626</v>
+        <v>754</v>
       </c>
     </row>
     <row r="234">
@@ -4293,7 +5061,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>627</v>
+        <v>755</v>
       </c>
     </row>
     <row r="235">
@@ -4301,7 +5069,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>628</v>
+        <v>756</v>
       </c>
     </row>
     <row r="236">
@@ -4309,7 +5077,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>629</v>
+        <v>757</v>
       </c>
     </row>
     <row r="237">
@@ -4317,7 +5085,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>630</v>
+        <v>758</v>
       </c>
     </row>
     <row r="238">
@@ -4325,7 +5093,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>631</v>
+        <v>759</v>
       </c>
     </row>
     <row r="239">
@@ -4333,7 +5101,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>632</v>
+        <v>760</v>
       </c>
     </row>
     <row r="240">
@@ -4341,7 +5109,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>633</v>
+        <v>761</v>
       </c>
     </row>
     <row r="241">
@@ -4349,7 +5117,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>634</v>
+        <v>762</v>
       </c>
     </row>
     <row r="242">
@@ -4357,7 +5125,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>635</v>
+        <v>763</v>
       </c>
     </row>
     <row r="243">
@@ -4365,7 +5133,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>636</v>
+        <v>764</v>
       </c>
     </row>
     <row r="244">
@@ -4373,7 +5141,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>637</v>
+        <v>765</v>
       </c>
     </row>
     <row r="245">
@@ -4381,7 +5149,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>638</v>
+        <v>766</v>
       </c>
     </row>
     <row r="246">
@@ -4389,7 +5157,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>639</v>
+        <v>767</v>
       </c>
     </row>
     <row r="247">
@@ -4397,7 +5165,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>640</v>
+        <v>768</v>
       </c>
     </row>
     <row r="248">
@@ -4405,7 +5173,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>641</v>
+        <v>769</v>
       </c>
     </row>
     <row r="249">
@@ -4413,7 +5181,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>642</v>
+        <v>770</v>
       </c>
     </row>
     <row r="250">
@@ -4421,7 +5189,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>643</v>
+        <v>771</v>
       </c>
     </row>
     <row r="251">
@@ -4429,7 +5197,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>644</v>
+        <v>772</v>
       </c>
     </row>
     <row r="252">
@@ -4437,7 +5205,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>645</v>
+        <v>773</v>
       </c>
     </row>
     <row r="253">
@@ -4445,7 +5213,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>646</v>
+        <v>774</v>
       </c>
     </row>
     <row r="254">
@@ -4453,7 +5221,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>647</v>
+        <v>775</v>
       </c>
     </row>
     <row r="255">
@@ -4461,7 +5229,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>648</v>
+        <v>776</v>
       </c>
     </row>
     <row r="256">
@@ -4469,7 +5237,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>649</v>
+        <v>777</v>
       </c>
     </row>
     <row r="257">
@@ -4477,7 +5245,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>650</v>
+        <v>778</v>
       </c>
     </row>
     <row r="258">
@@ -4485,7 +5253,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>651</v>
+        <v>779</v>
       </c>
     </row>
     <row r="259">
@@ -4493,7 +5261,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>652</v>
+        <v>780</v>
       </c>
     </row>
     <row r="260">
@@ -4501,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>653</v>
+        <v>781</v>
       </c>
     </row>
     <row r="261">
@@ -4509,7 +5277,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>654</v>
+        <v>782</v>
       </c>
     </row>
     <row r="262">
@@ -4517,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>655</v>
+        <v>783</v>
       </c>
     </row>
     <row r="263">
@@ -4525,7 +5293,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>656</v>
+        <v>784</v>
       </c>
     </row>
     <row r="264">
@@ -4533,7 +5301,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>657</v>
+        <v>785</v>
       </c>
     </row>
     <row r="265">
@@ -4541,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>658</v>
+        <v>786</v>
       </c>
     </row>
     <row r="266">
@@ -4549,7 +5317,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>659</v>
+        <v>787</v>
       </c>
     </row>
     <row r="267">
@@ -4557,7 +5325,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>660</v>
+        <v>788</v>
       </c>
     </row>
     <row r="268">
@@ -4565,7 +5333,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>661</v>
+        <v>789</v>
       </c>
     </row>
     <row r="269">
@@ -4573,7 +5341,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>662</v>
+        <v>790</v>
       </c>
     </row>
     <row r="270">
@@ -4581,7 +5349,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>663</v>
+        <v>791</v>
       </c>
     </row>
     <row r="271">
@@ -4589,7 +5357,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>664</v>
+        <v>792</v>
       </c>
     </row>
     <row r="272">
@@ -4597,7 +5365,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>665</v>
+        <v>793</v>
       </c>
     </row>
     <row r="273">
@@ -4605,7 +5373,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>666</v>
+        <v>794</v>
       </c>
     </row>
     <row r="274">
@@ -4613,7 +5381,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>667</v>
+        <v>795</v>
       </c>
     </row>
     <row r="275">
@@ -4621,7 +5389,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>668</v>
+        <v>796</v>
       </c>
     </row>
     <row r="276">
@@ -4629,7 +5397,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>669</v>
+        <v>797</v>
       </c>
     </row>
     <row r="277">
@@ -4637,7 +5405,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>670</v>
+        <v>798</v>
       </c>
     </row>
     <row r="278">
@@ -4645,7 +5413,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>671</v>
+        <v>799</v>
       </c>
     </row>
     <row r="279">
@@ -4653,7 +5421,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>672</v>
+        <v>800</v>
       </c>
     </row>
     <row r="280">
@@ -4661,7 +5429,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>673</v>
+        <v>801</v>
       </c>
     </row>
     <row r="281">
@@ -4669,7 +5437,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>674</v>
+        <v>802</v>
       </c>
     </row>
     <row r="282">
@@ -4677,7 +5445,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>675</v>
+        <v>803</v>
       </c>
     </row>
     <row r="283">
@@ -4685,7 +5453,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>676</v>
+        <v>804</v>
       </c>
     </row>
     <row r="284">
@@ -4693,7 +5461,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>677</v>
+        <v>805</v>
       </c>
     </row>
     <row r="285">
@@ -4701,7 +5469,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>678</v>
+        <v>806</v>
       </c>
     </row>
     <row r="286">
@@ -4709,7 +5477,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>679</v>
+        <v>807</v>
       </c>
     </row>
     <row r="287">
@@ -4717,7 +5485,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>680</v>
+        <v>808</v>
       </c>
     </row>
     <row r="288">
@@ -4725,7 +5493,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>681</v>
+        <v>809</v>
       </c>
     </row>
     <row r="289">
@@ -4733,7 +5501,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>682</v>
+        <v>810</v>
       </c>
     </row>
     <row r="290">
@@ -4741,7 +5509,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>683</v>
+        <v>811</v>
       </c>
     </row>
     <row r="291">
@@ -4749,7 +5517,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>684</v>
+        <v>812</v>
       </c>
     </row>
     <row r="292">
@@ -4757,7 +5525,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>685</v>
+        <v>813</v>
       </c>
     </row>
     <row r="293">
@@ -4765,7 +5533,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>686</v>
+        <v>814</v>
       </c>
     </row>
     <row r="294">
@@ -4773,7 +5541,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>687</v>
+        <v>815</v>
       </c>
     </row>
     <row r="295">
@@ -4781,7 +5549,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>688</v>
+        <v>816</v>
       </c>
     </row>
     <row r="296">
@@ -4789,7 +5557,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>689</v>
+        <v>817</v>
       </c>
     </row>
     <row r="297">
@@ -4797,7 +5565,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>690</v>
+        <v>818</v>
       </c>
     </row>
     <row r="298">
@@ -4805,7 +5573,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>691</v>
+        <v>819</v>
       </c>
     </row>
     <row r="299">
@@ -4813,7 +5581,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>692</v>
+        <v>820</v>
       </c>
     </row>
     <row r="300">
@@ -4821,7 +5589,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>693</v>
+        <v>821</v>
       </c>
     </row>
     <row r="301">
@@ -4829,7 +5597,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>694</v>
+        <v>822</v>
       </c>
     </row>
     <row r="302">
@@ -4837,7 +5605,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>695</v>
+        <v>823</v>
       </c>
     </row>
     <row r="303">
@@ -4845,7 +5613,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>696</v>
+        <v>824</v>
       </c>
     </row>
     <row r="304">
@@ -4853,7 +5621,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>697</v>
+        <v>825</v>
       </c>
     </row>
     <row r="305">
@@ -4861,7 +5629,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>698</v>
+        <v>826</v>
       </c>
     </row>
     <row r="306">
@@ -4869,7 +5637,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>699</v>
+        <v>827</v>
       </c>
     </row>
     <row r="307">
@@ -4877,7 +5645,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>700</v>
+        <v>828</v>
       </c>
     </row>
     <row r="308">
@@ -4885,7 +5653,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>701</v>
+        <v>829</v>
       </c>
     </row>
     <row r="309">
@@ -4893,7 +5661,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>702</v>
+        <v>830</v>
       </c>
     </row>
     <row r="310">
@@ -4901,7 +5669,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>703</v>
+        <v>831</v>
       </c>
     </row>
     <row r="311">
@@ -4909,7 +5677,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>704</v>
+        <v>832</v>
       </c>
     </row>
     <row r="312">
@@ -4917,7 +5685,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>705</v>
+        <v>833</v>
       </c>
     </row>
     <row r="313">
@@ -4925,7 +5693,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>706</v>
+        <v>834</v>
       </c>
     </row>
     <row r="314">
@@ -4933,7 +5701,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>707</v>
+        <v>835</v>
       </c>
     </row>
     <row r="315">
@@ -4941,7 +5709,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>708</v>
+        <v>836</v>
       </c>
     </row>
     <row r="316">
@@ -4949,7 +5717,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>709</v>
+        <v>837</v>
       </c>
     </row>
     <row r="317">
@@ -4957,7 +5725,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>710</v>
+        <v>838</v>
       </c>
     </row>
     <row r="318">
@@ -4965,7 +5733,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>711</v>
+        <v>839</v>
       </c>
     </row>
     <row r="319">
@@ -4973,7 +5741,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>712</v>
+        <v>840</v>
       </c>
     </row>
     <row r="320">
@@ -4981,7 +5749,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>713</v>
+        <v>841</v>
       </c>
     </row>
     <row r="321">
@@ -4989,7 +5757,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>714</v>
+        <v>842</v>
       </c>
     </row>
     <row r="322">
@@ -4997,7 +5765,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>715</v>
+        <v>843</v>
       </c>
     </row>
     <row r="323">
@@ -5005,7 +5773,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>716</v>
+        <v>844</v>
       </c>
     </row>
     <row r="324">
@@ -5013,7 +5781,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>717</v>
+        <v>845</v>
       </c>
     </row>
     <row r="325">
@@ -5021,7 +5789,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>718</v>
+        <v>846</v>
       </c>
     </row>
     <row r="326">
@@ -5029,7 +5797,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>719</v>
+        <v>847</v>
       </c>
     </row>
     <row r="327">
@@ -5037,7 +5805,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>720</v>
+        <v>848</v>
       </c>
     </row>
     <row r="328">
@@ -5045,7 +5813,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>721</v>
+        <v>849</v>
       </c>
     </row>
     <row r="329">
@@ -5053,7 +5821,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>722</v>
+        <v>850</v>
       </c>
     </row>
     <row r="330">
@@ -5061,7 +5829,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>723</v>
+        <v>851</v>
       </c>
     </row>
     <row r="331">
@@ -5069,7 +5837,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>724</v>
+        <v>852</v>
       </c>
     </row>
     <row r="332">
@@ -5077,7 +5845,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>725</v>
+        <v>853</v>
       </c>
     </row>
     <row r="333">
@@ -5085,7 +5853,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>726</v>
+        <v>854</v>
       </c>
     </row>
     <row r="334">
@@ -5093,7 +5861,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>727</v>
+        <v>855</v>
       </c>
     </row>
     <row r="335">
@@ -5101,7 +5869,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>728</v>
+        <v>856</v>
       </c>
     </row>
     <row r="336">
@@ -5109,7 +5877,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>729</v>
+        <v>857</v>
       </c>
     </row>
     <row r="337">
@@ -5117,7 +5885,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>730</v>
+        <v>858</v>
       </c>
     </row>
     <row r="338">
@@ -5125,7 +5893,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>731</v>
+        <v>859</v>
       </c>
     </row>
     <row r="339">
@@ -5133,7 +5901,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>732</v>
+        <v>860</v>
       </c>
     </row>
     <row r="340">
@@ -5141,7 +5909,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>733</v>
+        <v>861</v>
       </c>
     </row>
     <row r="341">
@@ -5149,7 +5917,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>734</v>
+        <v>862</v>
       </c>
     </row>
     <row r="342">
@@ -5157,7 +5925,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>735</v>
+        <v>863</v>
       </c>
     </row>
     <row r="343">
@@ -5165,7 +5933,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>736</v>
+        <v>864</v>
       </c>
     </row>
     <row r="344">
@@ -5173,7 +5941,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>737</v>
+        <v>865</v>
       </c>
     </row>
     <row r="345">
@@ -5181,7 +5949,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>738</v>
+        <v>866</v>
       </c>
     </row>
     <row r="346">
@@ -5189,7 +5957,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>739</v>
+        <v>867</v>
       </c>
     </row>
     <row r="347">
@@ -5197,7 +5965,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>740</v>
+        <v>868</v>
       </c>
     </row>
     <row r="348">
@@ -5205,7 +5973,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>741</v>
+        <v>869</v>
       </c>
     </row>
     <row r="349">
@@ -5213,7 +5981,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>742</v>
+        <v>870</v>
       </c>
     </row>
     <row r="350">
@@ -5221,7 +5989,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>743</v>
+        <v>871</v>
       </c>
     </row>
     <row r="351">
@@ -5229,7 +5997,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>744</v>
+        <v>872</v>
       </c>
     </row>
     <row r="352">
@@ -5237,7 +6005,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>745</v>
+        <v>873</v>
       </c>
     </row>
     <row r="353">
@@ -5245,7 +6013,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>746</v>
+        <v>874</v>
       </c>
     </row>
     <row r="354">
@@ -5253,7 +6021,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>747</v>
+        <v>875</v>
       </c>
     </row>
     <row r="355">
@@ -5261,7 +6029,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>748</v>
+        <v>876</v>
       </c>
     </row>
     <row r="356">
@@ -5269,7 +6037,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>749</v>
+        <v>877</v>
       </c>
     </row>
     <row r="357">
@@ -5277,7 +6045,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>750</v>
+        <v>878</v>
       </c>
     </row>
     <row r="358">
@@ -5285,7 +6053,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>751</v>
+        <v>879</v>
       </c>
     </row>
     <row r="359">
@@ -5293,7 +6061,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>752</v>
+        <v>880</v>
       </c>
     </row>
     <row r="360">
@@ -5301,7 +6069,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>753</v>
+        <v>881</v>
       </c>
     </row>
     <row r="361">
@@ -5309,7 +6077,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>754</v>
+        <v>882</v>
       </c>
     </row>
     <row r="362">
@@ -5317,7 +6085,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>755</v>
+        <v>883</v>
       </c>
     </row>
     <row r="363">
@@ -5325,7 +6093,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>756</v>
+        <v>884</v>
       </c>
     </row>
     <row r="364">
@@ -5333,7 +6101,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>757</v>
+        <v>885</v>
       </c>
     </row>
     <row r="365">
@@ -5341,7 +6109,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>758</v>
+        <v>886</v>
       </c>
     </row>
     <row r="366">
@@ -5349,7 +6117,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>759</v>
+        <v>887</v>
       </c>
     </row>
     <row r="367">
@@ -5357,7 +6125,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>760</v>
+        <v>888</v>
       </c>
     </row>
     <row r="368">
@@ -5365,7 +6133,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>761</v>
+        <v>889</v>
       </c>
     </row>
     <row r="369">
@@ -5373,7 +6141,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>762</v>
+        <v>890</v>
       </c>
     </row>
     <row r="370">
@@ -5381,7 +6149,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>763</v>
+        <v>891</v>
       </c>
     </row>
     <row r="371">
@@ -5389,7 +6157,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>764</v>
+        <v>892</v>
       </c>
     </row>
     <row r="372">
@@ -5397,7 +6165,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>765</v>
+        <v>893</v>
       </c>
     </row>
     <row r="373">
@@ -5405,7 +6173,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>766</v>
+        <v>894</v>
       </c>
     </row>
     <row r="374">
@@ -5413,7 +6181,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>767</v>
+        <v>895</v>
       </c>
     </row>
     <row r="375">
@@ -5421,7 +6189,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>768</v>
+        <v>896</v>
       </c>
     </row>
     <row r="376">
@@ -5429,7 +6197,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>769</v>
+        <v>897</v>
       </c>
     </row>
     <row r="377">
@@ -5437,7 +6205,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>770</v>
+        <v>898</v>
       </c>
     </row>
     <row r="378">
@@ -5445,7 +6213,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>771</v>
+        <v>899</v>
       </c>
     </row>
     <row r="379">
@@ -5453,7 +6221,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>772</v>
+        <v>900</v>
       </c>
     </row>
     <row r="380">
@@ -5461,7 +6229,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>773</v>
+        <v>901</v>
       </c>
     </row>
     <row r="381">
@@ -5469,7 +6237,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>774</v>
+        <v>902</v>
       </c>
     </row>
     <row r="382">
@@ -5477,7 +6245,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>775</v>
+        <v>903</v>
       </c>
     </row>
     <row r="383">
@@ -5485,7 +6253,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>776</v>
+        <v>904</v>
       </c>
     </row>
     <row r="384">
@@ -5493,7 +6261,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>777</v>
+        <v>905</v>
       </c>
     </row>
     <row r="385">
@@ -5501,7 +6269,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>778</v>
+        <v>906</v>
       </c>
     </row>
     <row r="386">
@@ -5509,7 +6277,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>779</v>
+        <v>907</v>
       </c>
     </row>
     <row r="387">
@@ -5517,7 +6285,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>780</v>
+        <v>908</v>
       </c>
     </row>
     <row r="388">
@@ -5525,7 +6293,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>781</v>
+        <v>909</v>
       </c>
     </row>
     <row r="389">
@@ -5533,7 +6301,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>782</v>
+        <v>910</v>
       </c>
     </row>
     <row r="390">
@@ -5541,7 +6309,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>783</v>
+        <v>911</v>
       </c>
     </row>
     <row r="391">
@@ -5549,7 +6317,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>784</v>
+        <v>912</v>
       </c>
     </row>
     <row r="392">
@@ -5557,7 +6325,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>785</v>
+        <v>913</v>
       </c>
     </row>
     <row r="393">
@@ -5565,7 +6333,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>786</v>
+        <v>914</v>
       </c>
     </row>
     <row r="394">
@@ -5573,7 +6341,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>787</v>
+        <v>915</v>
       </c>
     </row>
     <row r="395">
@@ -5581,7 +6349,1031 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>788</v>
+        <v>916</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>395</v>
+      </c>
+      <c r="B396" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>396</v>
+      </c>
+      <c r="B397" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>397</v>
+      </c>
+      <c r="B398" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>398</v>
+      </c>
+      <c r="B399" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>399</v>
+      </c>
+      <c r="B400" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>400</v>
+      </c>
+      <c r="B401" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>401</v>
+      </c>
+      <c r="B402" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>402</v>
+      </c>
+      <c r="B403" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>403</v>
+      </c>
+      <c r="B404" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>404</v>
+      </c>
+      <c r="B405" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>405</v>
+      </c>
+      <c r="B406" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>406</v>
+      </c>
+      <c r="B407" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>407</v>
+      </c>
+      <c r="B408" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>408</v>
+      </c>
+      <c r="B409" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>409</v>
+      </c>
+      <c r="B410" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>410</v>
+      </c>
+      <c r="B411" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>411</v>
+      </c>
+      <c r="B412" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>412</v>
+      </c>
+      <c r="B413" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>413</v>
+      </c>
+      <c r="B414" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>414</v>
+      </c>
+      <c r="B415" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>415</v>
+      </c>
+      <c r="B416" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>416</v>
+      </c>
+      <c r="B417" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>417</v>
+      </c>
+      <c r="B418" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>418</v>
+      </c>
+      <c r="B419" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>419</v>
+      </c>
+      <c r="B420" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>421</v>
+      </c>
+      <c r="B422" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>422</v>
+      </c>
+      <c r="B423" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>423</v>
+      </c>
+      <c r="B424" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>424</v>
+      </c>
+      <c r="B425" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>425</v>
+      </c>
+      <c r="B426" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>426</v>
+      </c>
+      <c r="B427" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>427</v>
+      </c>
+      <c r="B428" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>430</v>
+      </c>
+      <c r="B431" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>431</v>
+      </c>
+      <c r="B432" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>433</v>
+      </c>
+      <c r="B434" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>434</v>
+      </c>
+      <c r="B435" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>435</v>
+      </c>
+      <c r="B436" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>436</v>
+      </c>
+      <c r="B437" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>437</v>
+      </c>
+      <c r="B438" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>438</v>
+      </c>
+      <c r="B439" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>439</v>
+      </c>
+      <c r="B440" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>440</v>
+      </c>
+      <c r="B441" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>441</v>
+      </c>
+      <c r="B442" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>442</v>
+      </c>
+      <c r="B443" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>443</v>
+      </c>
+      <c r="B444" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>444</v>
+      </c>
+      <c r="B445" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>445</v>
+      </c>
+      <c r="B446" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>446</v>
+      </c>
+      <c r="B447" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>447</v>
+      </c>
+      <c r="B448" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>448</v>
+      </c>
+      <c r="B449" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>449</v>
+      </c>
+      <c r="B450" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>450</v>
+      </c>
+      <c r="B451" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>451</v>
+      </c>
+      <c r="B452" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>452</v>
+      </c>
+      <c r="B453" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>453</v>
+      </c>
+      <c r="B454" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>454</v>
+      </c>
+      <c r="B455" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>455</v>
+      </c>
+      <c r="B456" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>456</v>
+      </c>
+      <c r="B457" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>457</v>
+      </c>
+      <c r="B458" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>458</v>
+      </c>
+      <c r="B459" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>459</v>
+      </c>
+      <c r="B460" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>461</v>
+      </c>
+      <c r="B462" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>462</v>
+      </c>
+      <c r="B463" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>463</v>
+      </c>
+      <c r="B464" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>464</v>
+      </c>
+      <c r="B465" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>465</v>
+      </c>
+      <c r="B466" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>466</v>
+      </c>
+      <c r="B467" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>467</v>
+      </c>
+      <c r="B468" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>468</v>
+      </c>
+      <c r="B469" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>469</v>
+      </c>
+      <c r="B470" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>470</v>
+      </c>
+      <c r="B471" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>471</v>
+      </c>
+      <c r="B472" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>472</v>
+      </c>
+      <c r="B473" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>473</v>
+      </c>
+      <c r="B474" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>474</v>
+      </c>
+      <c r="B475" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>475</v>
+      </c>
+      <c r="B476" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>476</v>
+      </c>
+      <c r="B477" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>477</v>
+      </c>
+      <c r="B478" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>478</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>479</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>480</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>481</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>482</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>483</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>484</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>485</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>486</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>487</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>488</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>489</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>490</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s">
+        <v>491</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="s">
+        <v>492</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="s">
+        <v>493</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s">
+        <v>494</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="s">
+        <v>495</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="s">
+        <v>496</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="s">
+        <v>497</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="s">
+        <v>498</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="s">
+        <v>499</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="s">
+        <v>500</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="s">
+        <v>501</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="s">
+        <v>502</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="s">
+        <v>503</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="s">
+        <v>504</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="s">
+        <v>505</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>506</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="s">
+        <v>507</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="s">
+        <v>508</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s">
+        <v>509</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s">
+        <v>510</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>511</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
+        <v>512</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s">
+        <v>513</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="s">
+        <v>514</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s">
+        <v>515</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
+        <v>516</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="s">
+        <v>517</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="s">
+        <v>518</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s">
+        <v>519</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="s">
+        <v>520</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s">
+        <v>521</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>522</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
